--- a/dev/ValueSet-bc-address-validation-status-value-set.xlsx
+++ b/dev/ValueSet-bc-address-validation-status-value-set.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
